--- a/05_Machine_Learning/01_DataEngineering/GraduationProjects/FactoryTwo/ExcelTemplateStandards/DataEntry/03_Process_Losses.xlsx
+++ b/05_Machine_Learning/01_DataEngineering/GraduationProjects/FactoryTwo/ExcelTemplateStandards/DataEntry/03_Process_Losses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kandilglass20-my.sharepoint.com/personal/ahmed_fergany_kandilglass_com/Documents/Attachments/GitHub/Final_Learning_AI/05_Machine_Learning/01_DataEngineering/GraduationProjects/FactoryTwo/ExcelTemplateStandards/DataEntry/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_3A67357E0FA4E32223FE17EE50D7702AE6949137" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA46D515-917F-4919-8F84-3593EB30BF62}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="11_3A67357E0FA4E32223FE17EE50D7702AE6949137" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16D007DD-5765-4B8B-8D99-AB49F00E5074}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">LossesOutput!$A$4:$R$4</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -1127,7 +1127,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{766F7D33-4398-4C50-899F-BFFE853A95CE}" name="LossesOutput_Fact" displayName="LossesOutput_Fact" ref="A4:R144" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19" totalsRowBorderDxfId="18">
-  <autoFilter ref="A4:R144" xr:uid="{766F7D33-4398-4C50-899F-BFFE853A95CE}"/>
+  <autoFilter ref="A4:R144" xr:uid="{766F7D33-4398-4C50-899F-BFFE853A95CE}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="21"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{DE321148-20D7-453D-92FF-89622E2E7F55}" name="FactoryCode" dataDxfId="17"/>
     <tableColumn id="2" xr3:uid="{AE1D0F72-8B93-4589-9D0C-3B5E70715865}" name="LineNumber" dataDxfId="16"/>
@@ -1683,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="C6" s="14">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>33</v>
@@ -1695,43 +1701,43 @@
         <v>39</v>
       </c>
       <c r="G6" s="16">
-        <v>92535</v>
+        <v>290</v>
       </c>
       <c r="H6" s="17">
-        <v>2.8E-3</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="I6" s="17">
-        <v>8.0000000000000004E-4</v>
+        <v>1E-4</v>
       </c>
       <c r="J6" s="17">
-        <v>4.3E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="K6" s="17">
-        <v>6.7999999999999996E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="L6" s="17">
-        <v>6.4999999999999997E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="M6" s="17">
-        <v>5.4999999999999997E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="N6" s="17">
-        <v>7.1000000000000004E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="O6" s="17">
-        <v>5.0000000000000001E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="P6" s="17">
-        <v>6.1000000000000004E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="Q6" s="17">
-        <v>4.0000000000000001E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="R6" s="17">
-        <v>1.1999999999999999E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>29</v>
       </c>
@@ -1751,7 +1757,7 @@
         <v>39</v>
       </c>
       <c r="G7" s="16">
-        <v>36029</v>
+        <v>1002</v>
       </c>
       <c r="H7" s="17">
         <v>8.8000000000000005E-3</v>
@@ -1787,7 +1793,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>29</v>
       </c>
@@ -1843,7 +1849,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>29</v>
       </c>
@@ -1899,7 +1905,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>29</v>
       </c>
@@ -1955,7 +1961,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>29</v>
       </c>
@@ -2011,7 +2017,7 @@
         <v>9.7999999999999997E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>29</v>
       </c>
@@ -2067,7 +2073,7 @@
         <v>1.5299999999999999E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>29</v>
       </c>
@@ -2123,7 +2129,7 @@
         <v>5.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>29</v>
       </c>
@@ -2291,7 +2297,7 @@
         <v>2.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>29</v>
       </c>
@@ -2347,7 +2353,7 @@
         <v>5.8999999999999999E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>29</v>
       </c>
@@ -2403,7 +2409,7 @@
         <v>6.3E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>29</v>
       </c>
@@ -2459,7 +2465,7 @@
         <v>1.0699999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>29</v>
       </c>
@@ -2515,7 +2521,7 @@
         <v>2.3999999999999998E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>29</v>
       </c>
@@ -2571,7 +2577,7 @@
         <v>9.4999999999999998E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
@@ -2627,7 +2633,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>29</v>
       </c>
@@ -2683,7 +2689,7 @@
         <v>2.8E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>29</v>
       </c>
@@ -2851,7 +2857,7 @@
         <v>3.8E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>29</v>
       </c>
@@ -2907,7 +2913,7 @@
         <v>3.7000000000000002E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>29</v>
       </c>
@@ -2963,7 +2969,7 @@
         <v>1.1299999999999999E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>29</v>
       </c>
@@ -3019,7 +3025,7 @@
         <v>3.7000000000000002E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>29</v>
       </c>
@@ -3075,7 +3081,7 @@
         <v>3.3E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>29</v>
       </c>
@@ -3131,7 +3137,7 @@
         <v>9.4000000000000004E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>29</v>
       </c>
@@ -3187,7 +3193,7 @@
         <v>8.3999999999999995E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>29</v>
       </c>
@@ -3243,7 +3249,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
         <v>29</v>
       </c>
@@ -3411,7 +3417,7 @@
         <v>2.8999999999999998E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>29</v>
       </c>
@@ -3467,7 +3473,7 @@
         <v>5.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>29</v>
       </c>
@@ -3523,7 +3529,7 @@
         <v>1.0500000000000001E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>29</v>
       </c>
@@ -3579,7 +3585,7 @@
         <v>8.3999999999999995E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>29</v>
       </c>
@@ -3635,7 +3641,7 @@
         <v>3.3E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>29</v>
       </c>
@@ -3691,7 +3697,7 @@
         <v>7.6E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>29</v>
       </c>
@@ -3747,7 +3753,7 @@
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>29</v>
       </c>
@@ -3803,7 +3809,7 @@
         <v>2.2000000000000001E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
         <v>29</v>
       </c>
@@ -3971,7 +3977,7 @@
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
         <v>29</v>
       </c>
@@ -4027,7 +4033,7 @@
         <v>5.8999999999999999E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
         <v>29</v>
       </c>
@@ -4083,7 +4089,7 @@
         <v>5.9999999999999995E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>29</v>
       </c>
@@ -4139,7 +4145,7 @@
         <v>6.9999999999999999E-4</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
         <v>29</v>
       </c>
@@ -4195,7 +4201,7 @@
         <v>4.7000000000000002E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>29</v>
       </c>
@@ -4251,7 +4257,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
         <v>29</v>
       </c>
@@ -4307,7 +4313,7 @@
         <v>1.5100000000000001E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>29</v>
       </c>
@@ -4363,7 +4369,7 @@
         <v>1.1999999999999999E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
         <v>29</v>
       </c>
@@ -4531,7 +4537,7 @@
         <v>3.0999999999999999E-3</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
         <v>29</v>
       </c>
@@ -4587,7 +4593,7 @@
         <v>1.2999999999999999E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
         <v>29</v>
       </c>
@@ -4643,7 +4649,7 @@
         <v>1.09E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
         <v>29</v>
       </c>
@@ -4699,7 +4705,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
         <v>29</v>
       </c>
@@ -4755,7 +4761,7 @@
         <v>8.8999999999999999E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
         <v>29</v>
       </c>
@@ -4811,7 +4817,7 @@
         <v>8.8999999999999999E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
         <v>29</v>
       </c>
@@ -4867,7 +4873,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
         <v>29</v>
       </c>
@@ -4923,7 +4929,7 @@
         <v>9.1000000000000004E-3</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
         <v>29</v>
       </c>
@@ -5091,7 +5097,7 @@
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
         <v>29</v>
       </c>
@@ -5147,7 +5153,7 @@
         <v>7.3000000000000001E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="13" t="s">
         <v>29</v>
       </c>
@@ -5203,7 +5209,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
         <v>29</v>
       </c>
@@ -5259,7 +5265,7 @@
         <v>3.8999999999999998E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="13" t="s">
         <v>29</v>
       </c>
@@ -5315,7 +5321,7 @@
         <v>7.7000000000000002E-3</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="13" t="s">
         <v>29</v>
       </c>
@@ -5371,7 +5377,7 @@
         <v>3.3E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="13" t="s">
         <v>29</v>
       </c>
@@ -5427,7 +5433,7 @@
         <v>1.8E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
         <v>29</v>
       </c>
@@ -5483,7 +5489,7 @@
         <v>9.9000000000000008E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="13" t="s">
         <v>29</v>
       </c>
@@ -5651,7 +5657,7 @@
         <v>4.8999999999999998E-3</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="13" t="s">
         <v>29</v>
       </c>
@@ -5707,7 +5713,7 @@
         <v>1.43E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="13" t="s">
         <v>29</v>
       </c>
@@ -5763,7 +5769,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="13" t="s">
         <v>29</v>
       </c>
@@ -5819,7 +5825,7 @@
         <v>6.1000000000000004E-3</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="13" t="s">
         <v>29</v>
       </c>
@@ -5875,7 +5881,7 @@
         <v>4.4000000000000003E-3</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
         <v>29</v>
       </c>
@@ -5931,7 +5937,7 @@
         <v>4.1000000000000003E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="13" t="s">
         <v>29</v>
       </c>
@@ -5987,7 +5993,7 @@
         <v>2.3E-3</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="13" t="s">
         <v>29</v>
       </c>
@@ -6043,7 +6049,7 @@
         <v>8.8000000000000005E-3</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="13" t="s">
         <v>29</v>
       </c>
@@ -6211,7 +6217,7 @@
         <v>6.6E-3</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="13" t="s">
         <v>29</v>
       </c>
@@ -6267,7 +6273,7 @@
         <v>8.8000000000000005E-3</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="13" t="s">
         <v>29</v>
       </c>
@@ -6323,7 +6329,7 @@
         <v>6.1999999999999998E-3</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="13" t="s">
         <v>29</v>
       </c>
@@ -6379,7 +6385,7 @@
         <v>9.7000000000000003E-3</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="13" t="s">
         <v>29</v>
       </c>
@@ -6435,7 +6441,7 @@
         <v>9.1999999999999998E-3</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="13" t="s">
         <v>29</v>
       </c>
@@ -6491,7 +6497,7 @@
         <v>9.1000000000000004E-3</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="13" t="s">
         <v>29</v>
       </c>
@@ -6547,7 +6553,7 @@
         <v>1.3899999999999999E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="13" t="s">
         <v>29</v>
       </c>
@@ -6603,7 +6609,7 @@
         <v>6.7999999999999996E-3</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="13" t="s">
         <v>29</v>
       </c>
@@ -6771,7 +6777,7 @@
         <v>4.7999999999999996E-3</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="13" t="s">
         <v>29</v>
       </c>
@@ -6827,7 +6833,7 @@
         <v>5.9999999999999995E-4</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="13" t="s">
         <v>29</v>
       </c>
@@ -6883,7 +6889,7 @@
         <v>1.43E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
         <v>29</v>
       </c>
@@ -6939,7 +6945,7 @@
         <v>6.7000000000000002E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
         <v>29</v>
       </c>
@@ -6995,7 +7001,7 @@
         <v>4.3E-3</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="13" t="s">
         <v>29</v>
       </c>
@@ -7051,7 +7057,7 @@
         <v>7.6E-3</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="13" t="s">
         <v>29</v>
       </c>
@@ -7107,7 +7113,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="13" t="s">
         <v>29</v>
       </c>
@@ -7163,7 +7169,7 @@
         <v>2.3999999999999998E-3</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="13" t="s">
         <v>29</v>
       </c>
@@ -7331,7 +7337,7 @@
         <v>6.7000000000000002E-3</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="13" t="s">
         <v>29</v>
       </c>
@@ -7387,7 +7393,7 @@
         <v>5.3E-3</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="13" t="s">
         <v>29</v>
       </c>
@@ -7443,7 +7449,7 @@
         <v>1.0800000000000001E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="13" t="s">
         <v>29</v>
       </c>
@@ -7499,7 +7505,7 @@
         <v>6.9999999999999999E-4</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="13" t="s">
         <v>29</v>
       </c>
@@ -7555,7 +7561,7 @@
         <v>6.9999999999999999E-4</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="13" t="s">
         <v>29</v>
       </c>
@@ -7611,7 +7617,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="13" t="s">
         <v>29</v>
       </c>
@@ -7667,7 +7673,7 @@
         <v>5.4000000000000003E-3</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="13" t="s">
         <v>29</v>
       </c>
@@ -7723,7 +7729,7 @@
         <v>8.3999999999999995E-3</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="13" t="s">
         <v>29</v>
       </c>
@@ -7891,7 +7897,7 @@
         <v>5.1000000000000004E-3</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="13" t="s">
         <v>29</v>
       </c>
@@ -7947,7 +7953,7 @@
         <v>1.09E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="13" t="s">
         <v>29</v>
       </c>
@@ -8003,7 +8009,7 @@
         <v>5.8999999999999999E-3</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="13" t="s">
         <v>29</v>
       </c>
@@ -8059,7 +8065,7 @@
         <v>4.1999999999999997E-3</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="13" t="s">
         <v>29</v>
       </c>
@@ -8115,7 +8121,7 @@
         <v>4.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="13" t="s">
         <v>29</v>
       </c>
@@ -8171,7 +8177,7 @@
         <v>8.8000000000000005E-3</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="13" t="s">
         <v>29</v>
       </c>
@@ -8227,7 +8233,7 @@
         <v>5.8999999999999999E-3</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="13" t="s">
         <v>29</v>
       </c>
@@ -8283,7 +8289,7 @@
         <v>1.0200000000000001E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="13" t="s">
         <v>29</v>
       </c>
@@ -8451,7 +8457,7 @@
         <v>4.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="13" t="s">
         <v>29</v>
       </c>
@@ -8507,7 +8513,7 @@
         <v>8.8999999999999999E-3</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="13" t="s">
         <v>29</v>
       </c>
@@ -8563,7 +8569,7 @@
         <v>6.1999999999999998E-3</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="13" t="s">
         <v>29</v>
       </c>
@@ -8619,7 +8625,7 @@
         <v>4.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="13" t="s">
         <v>29</v>
       </c>
@@ -8675,7 +8681,7 @@
         <v>4.8999999999999998E-3</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="13" t="s">
         <v>29</v>
       </c>
@@ -8731,7 +8737,7 @@
         <v>9.9000000000000008E-3</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="13" t="s">
         <v>29</v>
       </c>
@@ -8787,7 +8793,7 @@
         <v>1.21E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="13" t="s">
         <v>29</v>
       </c>
@@ -8843,7 +8849,7 @@
         <v>5.1999999999999998E-3</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="13" t="s">
         <v>29</v>
       </c>
@@ -9011,7 +9017,7 @@
         <v>8.9999999999999998E-4</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="13" t="s">
         <v>29</v>
       </c>
@@ -9067,7 +9073,7 @@
         <v>3.3999999999999998E-3</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="13" t="s">
         <v>29</v>
       </c>
@@ -9123,7 +9129,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="13" t="s">
         <v>29</v>
       </c>
@@ -9179,7 +9185,7 @@
         <v>7.9000000000000008E-3</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="13" t="s">
         <v>29</v>
       </c>
@@ -9235,7 +9241,7 @@
         <v>5.4000000000000003E-3</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="13" t="s">
         <v>29</v>
       </c>
@@ -9291,7 +9297,7 @@
         <v>7.6E-3</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="13" t="s">
         <v>29</v>
       </c>
@@ -9347,7 +9353,7 @@
         <v>3.0999999999999999E-3</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="13" t="s">
         <v>29</v>
       </c>
@@ -9403,7 +9409,7 @@
         <v>2.3999999999999998E-3</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="13" t="s">
         <v>29</v>
       </c>
